--- a/reports/pdf_change_20260903.xlsx
+++ b/reports/pdf_change_20260903.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,489억   ·   현금 33억(0.7%)      당일 2026-09-03  vs  전영업일 2026-09-02      매수 5종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,425억      당일 2026-09-03  vs  전영업일 2026-09-02      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>876375000</v>
+        <v>874665000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-33</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2178330000</v>
+        <v>-2174079600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1260750000</v>
+        <v>1258290000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-22</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1637130000</v>
+        <v>-1633935600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>868380000</v>
+        <v>866685600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-7</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-408257500</v>
+        <v>-407460900</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>873812500</v>
+        <v>872107500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1236150000</v>
+        <v>1233738000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,768억   ·   현금 12억(0.3%)      당일 2026-09-03  vs  전영업일 2026-09-02      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,652억      당일 2026-09-03  vs  전영업일 2026-09-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -875,7 +875,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,513억   ·   현금 36억(1.5%)      당일 2026-09-03  vs  전영업일 2026-09-02      매수 2종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,471억      당일 2026-09-03  vs  전영업일 2026-09-02      매수 2종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -971,7 +971,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>507414600</v>
+        <v>506682400</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>294663600</v>
+        <v>294238400</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,141억   ·   현금 27억(1.3%)      당일 2026-09-03  vs  전영업일 2026-09-02      매수 1종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,065억      당일 2026-09-03  vs  전영업일 2026-09-02      매수 1종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1265,7 +1265,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 1억(0.5%)      당일 2026-09-03  vs  전영업일 2026-09-02      매수 1종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 262억      당일 2026-09-03  vs  전영업일 2026-09-02      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1361,11 +1361,11 @@
         <v>33</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>87436800</v>
+        <v>77154000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>7.21%→7.53%</t>
+          <t>6.68%→6.97%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1382,11 +1382,11 @@
         <v>-10</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-36720000</v>
+        <v>-35280000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>1.41%→1.28%</t>
+          <t>1.42%→1.29%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1410,11 +1410,11 @@
         <v>-9</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-26276400</v>
+        <v>-24948000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.83%→2.73%</t>
+          <t>2.82%→2.72%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 535억   ·   현금 4억(0.8%)      당일 2026-09-03  vs  전영업일 2026-09-02      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 523억      당일 2026-09-03  vs  전영업일 2026-09-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
